--- a/temp/BBVA_MASTERCARD_20250306.xlsx
+++ b/temp/BBVA_MASTERCARD_20250306.xlsx
@@ -471,8 +471,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-49846.4</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-49846,4</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -496,8 +498,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>138739.6</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>138739,6</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -521,8 +525,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>97000</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>97000,0</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -546,8 +552,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>7584.04</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7584,04</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -571,8 +579,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>107970</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>107970,0</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -596,8 +606,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>105070</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>105070,0</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -621,8 +633,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>27399.06</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>27399,06</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -646,8 +660,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>16000</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>16000,0</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -671,8 +687,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>2000</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2000,0</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -696,8 +714,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>4000</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4000,0</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -721,8 +741,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>2280</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2280,0</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
